--- a/database/template-import-export/templates/template-bantuan-korelasi.xlsx
+++ b/database/template-import-export/templates/template-bantuan-korelasi.xlsx
@@ -24,7 +24,7 @@
     <t>Korelasi nilai bantuan vs kenaikan produksi per sektor.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.34</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.44</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
